--- a/tests/fixtures/hostile_score/cf98e431_p50_01_sales_messy.xlsx
+++ b/tests/fixtures/hostile_score/cf98e431_p50_01_sales_messy.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,36 +595,6 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SKU-10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Misc</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SKU-11</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>900</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
